--- a/C题/p3/m1_out/m1_结果.xlsx
+++ b/C题/p3/m1_out/m1_结果.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,58 +429,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>MAE</t>
+          <t>MAE_kW</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>原始附件3 白天 整点</t>
+          <t>原始附件3 白天 全年(锚点复现)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>872.92</v>
+        <v>566.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>原始附件3 白天 10min</t>
+          <t>原始附件3 白天 334天</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>894.1799999999999</v>
+        <v>581.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EGD 白天 10min</t>
+          <t>矫正(W=28) 白天 全年</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>381.77</v>
+        <v>341.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>矫正(W=28) 白天 整点</t>
+          <t>矫正(W=28) 白天 334天</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>448.58</v>
+        <v>350.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>矫正(W=28) 白天 10min</t>
+          <t>EGD v5 白天 334天(整点)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>591.65</v>
+        <v>249.49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>敏感性: P1/P2时段口径 原始→矫正(334天)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>731.1 → 416.7</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -494,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,65 +517,117 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>白天MAE_整点</t>
+          <t>白天MAE_334天</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>白天MAE_10min</t>
+          <t>白天MAE_全年</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>448.58</v>
+        <v>355.8</v>
       </c>
       <c r="C2" t="n">
-        <v>591.65</v>
+        <v>346.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>458.47</v>
+        <v>349.68</v>
       </c>
       <c r="C3" t="n">
-        <v>594.83</v>
+        <v>340.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>469.66</v>
+        <v>349.15</v>
       </c>
       <c r="C4" t="n">
-        <v>601.5700000000001</v>
+        <v>340.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>350.32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>341.54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="C6" t="n">
+        <v>344.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="C7" t="n">
+        <v>348.56</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>356.92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>expanding</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>476.86</v>
-      </c>
-      <c r="C5" t="n">
-        <v>605.28</v>
+      <c r="B9" t="n">
+        <v>375.18</v>
+      </c>
+      <c r="C9" t="n">
+        <v>364.31</v>
       </c>
     </row>
   </sheetData>
@@ -588,22 +652,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>原始_白天</t>
+          <t>原始_全年</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>矫正_白天</t>
+          <t>矫正_全年</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>原始_全天</t>
+          <t>原始_334天</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>矫正_全天</t>
+          <t>矫正_334天</t>
         </is>
       </c>
     </row>
@@ -614,16 +678,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>848.2</v>
+        <v>544.9</v>
       </c>
       <c r="C2" t="n">
-        <v>425.4</v>
+        <v>323.9</v>
       </c>
       <c r="D2" t="n">
-        <v>444.6</v>
+        <v>559.7</v>
       </c>
       <c r="E2" t="n">
-        <v>217.5</v>
+        <v>332.9</v>
       </c>
     </row>
     <row r="3">
@@ -633,16 +697,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>778.4</v>
+        <v>480</v>
       </c>
       <c r="C3" t="n">
-        <v>282.5</v>
+        <v>207.2</v>
       </c>
       <c r="D3" t="n">
-        <v>409.9</v>
+        <v>490.6</v>
       </c>
       <c r="E3" t="n">
-        <v>147.3</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="4">
@@ -652,16 +716,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>925</v>
+        <v>612.1</v>
       </c>
       <c r="C4" t="n">
-        <v>517.5</v>
+        <v>391.7</v>
       </c>
       <c r="D4" t="n">
-        <v>483.2</v>
+        <v>628.2</v>
       </c>
       <c r="E4" t="n">
-        <v>264.1</v>
+        <v>403.7</v>
       </c>
     </row>
     <row r="5">
@@ -671,16 +735,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>940.4</v>
+        <v>629.8</v>
       </c>
       <c r="C5" t="n">
-        <v>569.4</v>
+        <v>443.6</v>
       </c>
       <c r="D5" t="n">
-        <v>490.3</v>
+        <v>645.8</v>
       </c>
       <c r="E5" t="n">
-        <v>289.5</v>
+        <v>452.4</v>
       </c>
     </row>
   </sheetData>
@@ -721,10 +785,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>793</v>
+        <v>471.5</v>
       </c>
       <c r="C2" t="n">
-        <v>213.4</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="3">
@@ -734,10 +798,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>769.1</v>
+        <v>501.8</v>
       </c>
       <c r="C3" t="n">
-        <v>337.2</v>
+        <v>259.1</v>
       </c>
     </row>
     <row r="4">
@@ -747,10 +811,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>969</v>
+        <v>670.5</v>
       </c>
       <c r="C4" t="n">
-        <v>601.5</v>
+        <v>479.4</v>
       </c>
     </row>
   </sheetData>
@@ -764,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,156 +839,208 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>原始</t>
+          <t>原始_全年</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>矫正</t>
+          <t>矫正_全年</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>矫正_334天</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>792.7</v>
+        <v>411.9</v>
       </c>
       <c r="C2" t="n">
-        <v>377.6</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>885.5</v>
+        <v>500</v>
       </c>
       <c r="C3" t="n">
-        <v>453.5</v>
+        <v>286.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>286.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>946.3</v>
+        <v>567.3</v>
       </c>
       <c r="C4" t="n">
-        <v>498.3</v>
+        <v>348.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>348.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>887.4</v>
+        <v>631.9</v>
       </c>
       <c r="C5" t="n">
-        <v>504</v>
+        <v>401.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>401.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>782.2</v>
+        <v>630.8</v>
       </c>
       <c r="C6" t="n">
-        <v>494.2</v>
+        <v>399</v>
+      </c>
+      <c r="D6" t="n">
+        <v>399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>863.3</v>
+        <v>573.9</v>
       </c>
       <c r="C7" t="n">
-        <v>482.4</v>
+        <v>383.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>383.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>7月</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>985.7</v>
+        <v>619.1</v>
       </c>
       <c r="C8" t="n">
-        <v>510.7</v>
+        <v>381.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>381.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1033</v>
+        <v>673.7</v>
       </c>
       <c r="C9" t="n">
-        <v>495.1</v>
+        <v>402.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>402.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>976.4</v>
+        <v>666.2</v>
       </c>
       <c r="C10" t="n">
-        <v>482.1</v>
+        <v>384.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>384.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>789.7</v>
+        <v>621.1</v>
       </c>
       <c r="C11" t="n">
-        <v>337.8</v>
+        <v>374.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>374.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>494.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>262</v>
+      </c>
+      <c r="D12" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>651.6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>291.1</v>
+      <c r="B13" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>222.2</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +1070,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>平均|偏差|</t>
+          <t>平均|滚动偏差|</t>
         </is>
       </c>
     </row>
@@ -966,11 +1082,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>726.6</v>
+        <v>445.2</v>
       </c>
     </row>
     <row r="3">
@@ -981,11 +1097,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>719.9</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4">
@@ -996,11 +1112,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>689.7</v>
+        <v>423.4</v>
       </c>
     </row>
     <row r="5">
@@ -1011,11 +1127,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>736.7</v>
+        <v>455.1</v>
       </c>
     </row>
   </sheetData>
